--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -14,13 +14,15 @@
     <sheet name="Include #4" r:id="rId8" sheetId="6"/>
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
     <sheet name="Include #6" r:id="rId10" sheetId="8"/>
-    <sheet name="Include ValueSet #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
+    <sheet name="Include ValueSet #9" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -184,16 +186,58 @@
     <t>DG20</t>
   </si>
   <si>
+    <t>DG834B</t>
+  </si>
+  <si>
+    <t>DI20</t>
+  </si>
+  <si>
+    <t>DI25</t>
+  </si>
+  <si>
+    <t>DI340</t>
+  </si>
+  <si>
+    <t>DI350</t>
+  </si>
+  <si>
+    <t>DI48</t>
+  </si>
+  <si>
+    <t>DI50</t>
+  </si>
+  <si>
+    <t>DI511A</t>
+  </si>
+  <si>
+    <t>DI719A</t>
+  </si>
+  <si>
+    <t>DI739A</t>
+  </si>
+  <si>
     <t>DJ44</t>
   </si>
   <si>
-    <t>DI20</t>
-  </si>
-  <si>
-    <t>DI25</t>
-  </si>
-  <si>
-    <t>DI50</t>
+    <t>DJ45</t>
+  </si>
+  <si>
+    <t>DM16</t>
+  </si>
+  <si>
+    <t>DM17</t>
+  </si>
+  <si>
+    <t>DM54</t>
+  </si>
+  <si>
+    <t>DQ231</t>
+  </si>
+  <si>
+    <t>DQ231A</t>
+  </si>
+  <si>
+    <t>DQ251</t>
   </si>
   <si>
     <t>DZ032</t>
@@ -205,6 +249,9 @@
     <t>DZ76</t>
   </si>
   <si>
+    <t>DZ952</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -214,6 +261,12 @@
     <t>urn:oid:1.2.208.176.2.4</t>
   </si>
   <si>
+    <t>413307004</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>Operation</t>
   </si>
   <si>
@@ -242,6 +295,18 @@
   </si>
   <si>
     <t>J5</t>
+  </si>
+  <si>
+    <t>I3.4</t>
+  </si>
+  <si>
+    <t>I6.4</t>
+  </si>
+  <si>
+    <t>I7.2</t>
+  </si>
+  <si>
+    <t>I9.3</t>
   </si>
   <si>
     <t>ValueSet URL</t>
@@ -509,9 +574,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -528,216 +593,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>63</v>
+        <v>77</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -745,9 +636,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -756,40 +647,382 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>64</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>67</v>
-      </c>
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>62</v>
       </c>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -819,29 +1052,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -863,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -871,29 +1104,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -923,29 +1156,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -975,29 +1208,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1019,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -1027,29 +1260,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1059,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1068,12 +1301,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>74</v>
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-conditions.xlsx
+++ b/fhir/ValueSet-ehealth-conditions.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
